--- a/IT23411562_Assignment 1 - Test cases.xlsx
+++ b/IT23411562_Assignment 1 - Test cases.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>UI Error</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>ඔයා මගේ tst@ml.c ඒකට msg එක දාන්න.</t>
+          <t>ඔයා මගේ ටේස්ට්.සී එකට msg එක දැන්.</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -3330,8 +3330,8 @@
   </sheetData>
   <mergeCells count="300">
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B66:B69"/>
     <mergeCell ref="C154:C157"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>

--- a/IT23411562_Assignment 1 - Test cases.xlsx
+++ b/IT23411562_Assignment 1 - Test cases.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -3330,8 +3330,8 @@
   </sheetData>
   <mergeCells count="300">
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C98:C101"/>
     <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C98:C101"/>
     <mergeCell ref="C154:C157"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>
